--- a/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
+++ b/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
@@ -1133,7 +1133,8 @@
         <is>
           <t>https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/
-https://thecybersec.gr/posts/purview-autolabeling-500k-scale-increase/</t>
+https://thecybersec.gr/posts/purview-autolabeling-500k-scale-increase/
+https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/</t>
         </is>
       </c>
       <c r="N4" s="8" t="n"/>
@@ -2358,7 +2359,9 @@
         <is>
           <t>https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/
+https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
+https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/</t>
         </is>
       </c>
       <c r="N23" s="8" t="n"/>
@@ -2694,7 +2697,9 @@
       <c r="M28" s="7" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
-https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/</t>
+https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
+https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
+https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/</t>
         </is>
       </c>
       <c r="N28" s="8" t="n"/>

--- a/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
+++ b/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,8 @@
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/</t>
+          <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
+https://thecybersec.gr/tekmiriosi-ekpaideysis/</t>
         </is>
       </c>
       <c r="N5" s="8" t="n"/>
@@ -2361,7 +2362,8 @@
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/
 https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
-https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/</t>
+https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/
+https://thecybersec.gr/posts/homograph-attack-kyrillika-grammata/</t>
         </is>
       </c>
       <c r="N23" s="8" t="n"/>
@@ -2628,7 +2630,12 @@
           <t>A.6.6, A.5.18</t>
         </is>
       </c>
-      <c r="M27" s="7" t="n"/>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/tekmiriosi-ekpaideysis/
+https://thecybersec.gr/kouiz-phishing/</t>
+        </is>
+      </c>
       <c r="N27" s="8" t="n"/>
       <c r="O27" s="8" t="n"/>
       <c r="P27" s="8" t="n"/>

--- a/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
+++ b/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,8 @@
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/
 https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
 https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/
-https://thecybersec.gr/posts/homograph-attack-kyrillika-grammata/</t>
+https://thecybersec.gr/posts/homograph-attack-kyrillika-grammata/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
         </is>
       </c>
       <c r="N23" s="8" t="n"/>
@@ -2706,7 +2707,8 @@
           <t>https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
 https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
-https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/</t>
+https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
         </is>
       </c>
       <c r="N28" s="8" t="n"/>

--- a/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
+++ b/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
@@ -2030,7 +2030,11 @@
           <t>A.5.19, A.5.21, A.5.23</t>
         </is>
       </c>
-      <c r="M18" s="7" t="n"/>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
+        </is>
+      </c>
       <c r="N18" s="8" t="n"/>
       <c r="O18" s="8" t="n"/>
       <c r="P18" s="8" t="n"/>
@@ -3230,7 +3234,11 @@
           <t>A.5.14, A.5.23</t>
         </is>
       </c>
-      <c r="M36" s="7" t="n"/>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
+        </is>
+      </c>
       <c r="N36" s="8" t="n"/>
       <c r="O36" s="8" t="n"/>
       <c r="P36" s="8" t="n"/>

--- a/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
+++ b/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
@@ -1204,8 +1204,9 @@
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
-https://thecybersec.gr/tekmiriosi-ekpaideysis/</t>
+          <t xml:space="preserve">https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
+https://thecybersec.gr/tekmiriosi-ekpaideysis/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="N5" s="8" t="n"/>
@@ -1829,8 +1830,9 @@
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
-https://thecybersec.gr/posts/secure-score-defender-praktikos-odigos/</t>
+          <t xml:space="preserve">https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
+https://thecybersec.gr/posts/secure-score-defender-praktikos-odigos/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="N15" s="8" t="n"/>

--- a/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
+++ b/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
+          <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
 https://thecybersec.gr/tekmiriosi-ekpaideysis/
 https://thecybersec.gr/mitroo-politikon/</t>
         </is>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
+          <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
 https://thecybersec.gr/posts/secure-score-defender-praktikos-odigos/
 https://thecybersec.gr/mitroo-politikon/</t>
         </is>
@@ -2714,7 +2714,8 @@
 https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
 https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/
+https://thecybersec.gr/posts/previews/isoc-sentinel-defender-xdr-poio-epilegeis/</t>
         </is>
       </c>
       <c r="N28" s="8" t="n"/>

--- a/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
+++ b/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,8 @@
 https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
 https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/
 https://thecybersec.gr/posts/homograph-attack-kyrillika-grammata/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/
+https://thecybersec.gr/giati-pige-sta-junk/</t>
         </is>
       </c>
       <c r="N23" s="8" t="n"/>

--- a/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
+++ b/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,8 @@
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
+          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/
 https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/

--- a/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
+++ b/static/downloads/gdpr-2016-679-microsoft-365-checklist.xlsx
@@ -2364,7 +2364,8 @@
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+          <t>https://thecybersec.gr/ti-simainei-aadsts/
+https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
 https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/
